--- a/tests/testdata/excel/機能.xlsx
+++ b/tests/testdata/excel/機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF4F7B01-0A5F-48C2-AF6E-DC32E9FB9300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC16BFA-29D7-43CA-97B8-3C7E79F3DC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" activeTab="3" xr2:uid="{3522D545-2A8D-4226-94C8-8960F189E528}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" activeTab="3" xr2:uid="{E2673CA8-6510-461A-8286-EB095ADFE369}"/>
   </bookViews>
   <sheets>
     <sheet name="名前と数式" sheetId="1" r:id="rId1"/>
@@ -313,7 +313,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="test" refreshedDate="46285.316325925924" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{FD9F5945-0FD6-49AB-9513-08D35BD377B2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="test" refreshedDate="46285.396016319442" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{A7F4EA33-C3F9-48B8-83DA-4CFAC659EF34}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D13" sheet="テーブルとピボット"/>
   </cacheSource>
@@ -421,7 +421,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63EFC266-ED9B-4827-9436-7AF0393BC62E}" name="TC24ピボット" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{120C2EBC-FE04-477E-AB9B-6A56101E3BFE}" name="TC24ピボット" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField numFmtId="14" showAll="0"/>
@@ -477,13 +477,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{512D6C52-E8A7-451F-A4AE-70BE477D391B}" name="売上テーブル" displayName="売上テーブル" ref="A1:D13" totalsRowShown="0">
-  <autoFilter ref="A1:D13" xr:uid="{512D6C52-E8A7-451F-A4AE-70BE477D391B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1018DB89-30D4-43C6-A8FB-B1DE3DBF56E2}" name="売上テーブル" displayName="売上テーブル" ref="A1:D13" totalsRowShown="0">
+  <autoFilter ref="A1:D13" xr:uid="{1018DB89-30D4-43C6-A8FB-B1DE3DBF56E2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{739284B5-A6DA-4DD8-ACB4-9B2F740FB6EC}" name="日付" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{1C9958DF-4526-4205-843B-BA841709E6B4}" name="支店"/>
-    <tableColumn id="3" xr3:uid="{AC6BEF2A-6DE7-40DB-9F82-D60E435F9BCC}" name="商品"/>
-    <tableColumn id="4" xr3:uid="{ECCCAF20-34DB-4AEE-9021-D792B0E7D01F}" name="金額"/>
+    <tableColumn id="1" xr3:uid="{E9FCA9FF-CF7C-4444-977B-B4A251794879}" name="日付" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{0065FF2E-B562-4371-8218-0B157232CEAD}" name="支店"/>
+    <tableColumn id="3" xr3:uid="{840F3202-8D1E-45D4-8CF7-842489F306C8}" name="商品"/>
+    <tableColumn id="4" xr3:uid="{887B54AE-9957-4E4D-9D30-22B0252C345A}" name="金額"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -805,7 +805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207C6CF5-9F1D-4757-ABB7-88A777A8C218}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C4ADBE-401A-4E4B-A02B-90AA3D48BFB9}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -978,7 +978,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3166870A-D07F-4E9A-A6C0-BA603C1DB764}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6B6E00-6540-44BC-98B7-1D0E0DF0090C}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
@@ -1068,7 +1068,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC14AF8C-8683-4F53-8D0A-3D48EA6733FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA456ED6-71AD-4ACE-961D-DC3EEF445EC5}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1159,7 +1159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AC5E09-13E6-4876-AEBF-89548C065AF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA659F7-18B8-46CD-A7DC-75CC60FDA3CC}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
